--- a/results/tablice/sve_tablice_rezultata.xlsx
+++ b/results/tablice/sve_tablice_rezultata.xlsx
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.144761</v>
+        <v>1.198896</v>
       </c>
       <c r="G26" t="n">
-        <v>1.38463</v>
+        <v>1.45074</v>
       </c>
       <c r="H26" t="n">
-        <v>0.228051</v>
+        <v>0.152577</v>
       </c>
       <c r="I26" t="n">
         <v>115</v>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.806596</v>
+        <v>1.806566</v>
       </c>
       <c r="G34" t="n">
-        <v>2.338891</v>
+        <v>2.338855</v>
       </c>
       <c r="H34" t="n">
-        <v>-8.150543000000001</v>
+        <v>-8.150264999999999</v>
       </c>
       <c r="I34" t="n">
         <v>144</v>
@@ -2639,13 +2639,13 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1.828572</v>
+        <v>1.828461</v>
       </c>
       <c r="G58" t="n">
-        <v>2.201069</v>
+        <v>2.200969</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.174731</v>
+        <v>-0.174625</v>
       </c>
       <c r="I58" t="n">
         <v>230</v>
@@ -2943,13 +2943,13 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0.219478</v>
+        <v>0.181154</v>
       </c>
       <c r="G66" t="n">
-        <v>0.276524</v>
+        <v>0.231963</v>
       </c>
       <c r="H66" t="n">
-        <v>0.670743</v>
+        <v>0.768311</v>
       </c>
       <c r="I66" t="n">
         <v>29</v>
@@ -3247,13 +3247,13 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>0.410821</v>
+        <v>0.307639</v>
       </c>
       <c r="G74" t="n">
-        <v>0.450142</v>
+        <v>0.351382</v>
       </c>
       <c r="H74" t="n">
-        <v>0.551572</v>
+        <v>0.726755</v>
       </c>
       <c r="I74" t="n">
         <v>58</v>
@@ -3551,13 +3551,13 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>0.667062</v>
+        <v>0.764224</v>
       </c>
       <c r="G82" t="n">
-        <v>0.769711</v>
+        <v>0.868886</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.406269</v>
+        <v>-0.792005</v>
       </c>
       <c r="I82" t="n">
         <v>86</v>
@@ -3855,13 +3855,13 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>2.923715</v>
+        <v>2.37209</v>
       </c>
       <c r="G90" t="n">
-        <v>3.250883</v>
+        <v>2.662934</v>
       </c>
       <c r="H90" t="n">
-        <v>-17.355148</v>
+        <v>-11.316183</v>
       </c>
       <c r="I90" t="n">
         <v>115</v>
@@ -4159,13 +4159,13 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>6.349068</v>
+        <v>4.536216</v>
       </c>
       <c r="G98" t="n">
-        <v>6.949935</v>
+        <v>5.05184</v>
       </c>
       <c r="H98" t="n">
-        <v>-79.24972099999999</v>
+        <v>-41.401493</v>
       </c>
       <c r="I98" t="n">
         <v>144</v>
@@ -4463,13 +4463,13 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>0.722704</v>
+        <v>0.80515</v>
       </c>
       <c r="G106" t="n">
-        <v>0.818569</v>
+        <v>0.992051</v>
       </c>
       <c r="H106" t="n">
-        <v>-0.049125</v>
+        <v>-0.540933</v>
       </c>
       <c r="I106" t="n">
         <v>173</v>
@@ -4767,13 +4767,13 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>2.646819</v>
+        <v>1.927389</v>
       </c>
       <c r="G114" t="n">
-        <v>3.187375</v>
+        <v>2.234575</v>
       </c>
       <c r="H114" t="n">
-        <v>-11.400049</v>
+        <v>-5.094623</v>
       </c>
       <c r="I114" t="n">
         <v>202</v>
@@ -5071,13 +5071,13 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>6.466504</v>
+        <v>4.038971</v>
       </c>
       <c r="G122" t="n">
-        <v>7.334357</v>
+        <v>4.886624</v>
       </c>
       <c r="H122" t="n">
-        <v>-35.167564</v>
+        <v>-15.055103</v>
       </c>
       <c r="I122" t="n">
         <v>230</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>0.536873</v>
+        <v>0.48059</v>
       </c>
       <c r="G194" t="n">
-        <v>0.6085199999999999</v>
+        <v>0.55072</v>
       </c>
       <c r="H194" t="n">
-        <v>-0.387975</v>
+        <v>-0.136827</v>
       </c>
       <c r="I194" t="n">
         <v>29</v>
@@ -8111,13 +8111,13 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>0.931054</v>
+        <v>1.03311</v>
       </c>
       <c r="G202" t="n">
-        <v>1.095394</v>
+        <v>1.209252</v>
       </c>
       <c r="H202" t="n">
-        <v>-1.250442</v>
+        <v>-1.742593</v>
       </c>
       <c r="I202" t="n">
         <v>58</v>
@@ -8415,13 +8415,13 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>0.971258</v>
+        <v>1.112531</v>
       </c>
       <c r="G210" t="n">
-        <v>1.194274</v>
+        <v>1.358855</v>
       </c>
       <c r="H210" t="n">
-        <v>-0.021377</v>
+        <v>-0.322284</v>
       </c>
       <c r="I210" t="n">
         <v>86</v>
@@ -8719,13 +8719,13 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>2.289966</v>
+        <v>1.944027</v>
       </c>
       <c r="G218" t="n">
-        <v>2.557596</v>
+        <v>2.161361</v>
       </c>
       <c r="H218" t="n">
-        <v>-1.710781</v>
+        <v>-0.93591</v>
       </c>
       <c r="I218" t="n">
         <v>115</v>
@@ -9023,13 +9023,13 @@
         </is>
       </c>
       <c r="F226" t="n">
-        <v>1.121923</v>
+        <v>1.043958</v>
       </c>
       <c r="G226" t="n">
-        <v>1.411519</v>
+        <v>1.325014</v>
       </c>
       <c r="H226" t="n">
-        <v>0.349667</v>
+        <v>0.426935</v>
       </c>
       <c r="I226" t="n">
         <v>144</v>
@@ -9327,13 +9327,13 @@
         </is>
       </c>
       <c r="F234" t="n">
-        <v>3.085711</v>
+        <v>2.457923</v>
       </c>
       <c r="G234" t="n">
-        <v>3.679453</v>
+        <v>2.860222</v>
       </c>
       <c r="H234" t="n">
-        <v>-3.126948</v>
+        <v>-1.493802</v>
       </c>
       <c r="I234" t="n">
         <v>173</v>
@@ -9631,13 +9631,13 @@
         </is>
       </c>
       <c r="F242" t="n">
-        <v>2.193331</v>
+        <v>1.676155</v>
       </c>
       <c r="G242" t="n">
-        <v>2.32589</v>
+        <v>1.77132</v>
       </c>
       <c r="H242" t="n">
-        <v>-0.616617</v>
+        <v>0.062388</v>
       </c>
       <c r="I242" t="n">
         <v>202</v>
@@ -9935,13 +9935,13 @@
         </is>
       </c>
       <c r="F250" t="n">
-        <v>0.882981</v>
+        <v>1.030693</v>
       </c>
       <c r="G250" t="n">
-        <v>1.102841</v>
+        <v>1.223813</v>
       </c>
       <c r="H250" t="n">
-        <v>0.694529</v>
+        <v>0.623838</v>
       </c>
       <c r="I250" t="n">
         <v>230</v>
@@ -10239,10 +10239,10 @@
         </is>
       </c>
       <c r="F258" t="n">
-        <v>0.0406</v>
+        <v>0.040592</v>
       </c>
       <c r="G258" t="n">
-        <v>0.050289</v>
+        <v>0.050278</v>
       </c>
       <c r="H258" t="n">
         <v>0.999283</v>
@@ -10543,10 +10543,10 @@
         </is>
       </c>
       <c r="F266" t="n">
-        <v>0.048762</v>
+        <v>0.048758</v>
       </c>
       <c r="G266" t="n">
-        <v>0.06723999999999999</v>
+        <v>0.067235</v>
       </c>
       <c r="H266" t="n">
         <v>0.9986660000000001</v>
@@ -10847,10 +10847,10 @@
         </is>
       </c>
       <c r="F274" t="n">
-        <v>0.044815</v>
+        <v>0.04482</v>
       </c>
       <c r="G274" t="n">
-        <v>0.060635</v>
+        <v>0.060632</v>
       </c>
       <c r="H274" t="n">
         <v>0.99907</v>
@@ -11151,13 +11151,13 @@
         </is>
       </c>
       <c r="F282" t="n">
-        <v>0.084856</v>
+        <v>0.084893</v>
       </c>
       <c r="G282" t="n">
-        <v>0.142062</v>
+        <v>0.14191</v>
       </c>
       <c r="H282" t="n">
-        <v>0.995285</v>
+        <v>0.995295</v>
       </c>
       <c r="I282" t="n">
         <v>115</v>
@@ -11455,13 +11455,13 @@
         </is>
       </c>
       <c r="F290" t="n">
-        <v>0.07883900000000001</v>
+        <v>0.078573</v>
       </c>
       <c r="G290" t="n">
-        <v>0.130379</v>
+        <v>0.130034</v>
       </c>
       <c r="H290" t="n">
-        <v>0.995847</v>
+        <v>0.995869</v>
       </c>
       <c r="I290" t="n">
         <v>144</v>
@@ -11759,13 +11759,13 @@
         </is>
       </c>
       <c r="F298" t="n">
-        <v>0.087632</v>
+        <v>0.087411</v>
       </c>
       <c r="G298" t="n">
-        <v>0.132136</v>
+        <v>0.131854</v>
       </c>
       <c r="H298" t="n">
-        <v>0.995954</v>
+        <v>0.9959710000000001</v>
       </c>
       <c r="I298" t="n">
         <v>173</v>
@@ -12063,13 +12063,13 @@
         </is>
       </c>
       <c r="F306" t="n">
-        <v>0.091271</v>
+        <v>0.091156</v>
       </c>
       <c r="G306" t="n">
-        <v>0.136509</v>
+        <v>0.136413</v>
       </c>
       <c r="H306" t="n">
-        <v>0.995627</v>
+        <v>0.995633</v>
       </c>
       <c r="I306" t="n">
         <v>202</v>
@@ -12367,13 +12367,13 @@
         </is>
       </c>
       <c r="F314" t="n">
-        <v>0.105574</v>
+        <v>0.10548</v>
       </c>
       <c r="G314" t="n">
-        <v>0.156678</v>
+        <v>0.15663</v>
       </c>
       <c r="H314" t="n">
-        <v>0.994362</v>
+        <v>0.9943650000000001</v>
       </c>
       <c r="I314" t="n">
         <v>230</v>
@@ -12755,17 +12755,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>cubic_interpolation</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.494712</v>
+        <v>0.48059</v>
       </c>
       <c r="D4" t="n">
-        <v>0.589221</v>
+        <v>0.55072</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.301332</v>
+        <v>-0.136827</v>
       </c>
       <c r="F4" t="n">
         <v>29</v>
@@ -12780,17 +12780,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>cubic_interpolation</t>
+          <t>random_forest</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.536873</v>
+        <v>0.494712</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6085199999999999</v>
+        <v>0.589221</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.387975</v>
+        <v>-0.301332</v>
       </c>
       <c r="F5" t="n">
         <v>29</v>
@@ -12930,7 +12930,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>cubic_interpolation</t>
+          <t>spline_interpolation</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -12955,17 +12955,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>spline_interpolation</t>
+          <t>random_forest</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.931054</v>
+        <v>1.016144</v>
       </c>
       <c r="D12" t="n">
-        <v>1.095394</v>
+        <v>1.193357</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.250442</v>
+        <v>-1.670966</v>
       </c>
       <c r="F12" t="n">
         <v>58</v>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>cubic_interpolation</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.016144</v>
+        <v>1.03311</v>
       </c>
       <c r="D13" t="n">
-        <v>1.193357</v>
+        <v>1.209252</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.670966</v>
+        <v>-1.742593</v>
       </c>
       <c r="F13" t="n">
         <v>58</v>
@@ -13105,7 +13105,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>cubic_interpolation</t>
+          <t>spline_interpolation</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -13130,17 +13130,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>spline_interpolation</t>
+          <t>forward_fill</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.971258</v>
+        <v>1.005698</v>
       </c>
       <c r="D19" t="n">
-        <v>1.194274</v>
+        <v>1.182391</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.021377</v>
+        <v>-0.001152</v>
       </c>
       <c r="F19" t="n">
         <v>86</v>
@@ -13155,17 +13155,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>forward_fill</t>
+          <t>cubic_interpolation</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.005698</v>
+        <v>1.112531</v>
       </c>
       <c r="D20" t="n">
-        <v>1.182391</v>
+        <v>1.358855</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.001152</v>
+        <v>-0.322284</v>
       </c>
       <c r="F20" t="n">
         <v>86</v>
@@ -13434,13 +13434,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2.289966</v>
+        <v>1.944027</v>
       </c>
       <c r="D31" t="n">
-        <v>2.557596</v>
+        <v>2.161361</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.710781</v>
+        <v>-0.93591</v>
       </c>
       <c r="F31" t="n">
         <v>115</v>
@@ -13559,13 +13559,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1.121923</v>
+        <v>1.043958</v>
       </c>
       <c r="D36" t="n">
-        <v>1.411519</v>
+        <v>1.325014</v>
       </c>
       <c r="E36" t="n">
-        <v>0.349667</v>
+        <v>0.426935</v>
       </c>
       <c r="F36" t="n">
         <v>144</v>
@@ -13830,17 +13830,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>cubic_interpolation</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2.471959</v>
+        <v>2.457923</v>
       </c>
       <c r="D47" t="n">
-        <v>2.907756</v>
+        <v>2.860222</v>
       </c>
       <c r="E47" t="n">
-        <v>-1.577379</v>
+        <v>-1.493802</v>
       </c>
       <c r="F47" t="n">
         <v>173</v>
@@ -13855,17 +13855,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>cubic_interpolation</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3.085711</v>
+        <v>2.471959</v>
       </c>
       <c r="D48" t="n">
-        <v>3.679453</v>
+        <v>2.907756</v>
       </c>
       <c r="E48" t="n">
-        <v>-3.126948</v>
+        <v>-1.577379</v>
       </c>
       <c r="F48" t="n">
         <v>173</v>
@@ -13955,17 +13955,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>cubic_interpolation</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2.078016</v>
+        <v>1.676155</v>
       </c>
       <c r="D52" t="n">
-        <v>2.313465</v>
+        <v>1.77132</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.599392</v>
+        <v>0.062388</v>
       </c>
       <c r="F52" t="n">
         <v>202</v>
@@ -13980,17 +13980,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>decision_tree</t>
+          <t>random_forest</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2.083729</v>
+        <v>2.078016</v>
       </c>
       <c r="D53" t="n">
-        <v>2.615003</v>
+        <v>2.313465</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.043494</v>
+        <v>-0.599392</v>
       </c>
       <c r="F53" t="n">
         <v>202</v>
@@ -14005,17 +14005,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>cubic_interpolation</t>
+          <t>decision_tree</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2.193331</v>
+        <v>2.083729</v>
       </c>
       <c r="D54" t="n">
-        <v>2.32589</v>
+        <v>2.615003</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.616617</v>
+        <v>-1.043494</v>
       </c>
       <c r="F54" t="n">
         <v>202</v>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>cubic_interpolation</t>
+          <t>spline_interpolation</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -14180,17 +14180,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>spline_interpolation</t>
+          <t>cubic_interpolation</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.882981</v>
+        <v>1.030693</v>
       </c>
       <c r="D61" t="n">
-        <v>1.102841</v>
+        <v>1.223813</v>
       </c>
       <c r="E61" t="n">
-        <v>0.694529</v>
+        <v>0.623838</v>
       </c>
       <c r="F61" t="n">
         <v>230</v>
@@ -14460,28 +14460,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.536873</v>
+        <v>0.48059</v>
       </c>
       <c r="C5" t="n">
-        <v>0.931054</v>
+        <v>1.03311</v>
       </c>
       <c r="D5" t="n">
-        <v>0.971258</v>
+        <v>1.112531</v>
       </c>
       <c r="E5" t="n">
-        <v>2.289966</v>
+        <v>1.944027</v>
       </c>
       <c r="F5" t="n">
-        <v>1.121923</v>
+        <v>1.043958</v>
       </c>
       <c r="G5" t="n">
-        <v>3.085711</v>
+        <v>2.457923</v>
       </c>
       <c r="H5" t="n">
-        <v>2.193331</v>
+        <v>1.676155</v>
       </c>
       <c r="I5" t="n">
-        <v>0.882981</v>
+        <v>1.030693</v>
       </c>
     </row>
     <row r="6">
@@ -14769,28 +14769,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6085199999999999</v>
+        <v>0.55072</v>
       </c>
       <c r="C5" t="n">
-        <v>1.095394</v>
+        <v>1.209252</v>
       </c>
       <c r="D5" t="n">
-        <v>1.194274</v>
+        <v>1.358855</v>
       </c>
       <c r="E5" t="n">
-        <v>2.557596</v>
+        <v>2.161361</v>
       </c>
       <c r="F5" t="n">
-        <v>1.411519</v>
+        <v>1.325014</v>
       </c>
       <c r="G5" t="n">
-        <v>3.679453</v>
+        <v>2.860222</v>
       </c>
       <c r="H5" t="n">
-        <v>2.32589</v>
+        <v>1.77132</v>
       </c>
       <c r="I5" t="n">
-        <v>1.102841</v>
+        <v>1.223813</v>
       </c>
     </row>
     <row r="6">
@@ -15078,28 +15078,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.387975</v>
+        <v>-0.136827</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.250442</v>
+        <v>-1.742593</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.021377</v>
+        <v>-0.322284</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.710781</v>
+        <v>-0.93591</v>
       </c>
       <c r="F5" t="n">
-        <v>0.349667</v>
+        <v>0.426935</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.126948</v>
+        <v>-1.493802</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.616617</v>
+        <v>0.062388</v>
       </c>
       <c r="I5" t="n">
-        <v>0.694529</v>
+        <v>0.623838</v>
       </c>
     </row>
     <row r="6">
@@ -17861,17 +17861,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>linear_interpolation</t>
+          <t>cubic_interpolation</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.196977</v>
+        <v>0.181154</v>
       </c>
       <c r="D2" t="n">
-        <v>0.252333</v>
+        <v>0.231963</v>
       </c>
       <c r="E2" t="n">
-        <v>0.725832</v>
+        <v>0.768311</v>
       </c>
       <c r="F2" t="n">
         <v>29</v>
@@ -17886,7 +17886,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>time_interpolation</t>
+          <t>linear_interpolation</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -17911,17 +17911,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>cubic_interpolation</t>
+          <t>time_interpolation</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.219478</v>
+        <v>0.196977</v>
       </c>
       <c r="D4" t="n">
-        <v>0.276524</v>
+        <v>0.252333</v>
       </c>
       <c r="E4" t="n">
-        <v>0.670743</v>
+        <v>0.725832</v>
       </c>
       <c r="F4" t="n">
         <v>29</v>
@@ -18061,17 +18061,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>linear_interpolation</t>
+          <t>cubic_interpolation</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.353793</v>
+        <v>0.307639</v>
       </c>
       <c r="D10" t="n">
-        <v>0.394</v>
+        <v>0.351382</v>
       </c>
       <c r="E10" t="n">
-        <v>0.656453</v>
+        <v>0.726755</v>
       </c>
       <c r="F10" t="n">
         <v>58</v>
@@ -18086,7 +18086,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>time_interpolation</t>
+          <t>linear_interpolation</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -18111,17 +18111,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>cubic_interpolation</t>
+          <t>time_interpolation</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.410821</v>
+        <v>0.353793</v>
       </c>
       <c r="D12" t="n">
-        <v>0.450142</v>
+        <v>0.394</v>
       </c>
       <c r="E12" t="n">
-        <v>0.551572</v>
+        <v>0.656453</v>
       </c>
       <c r="F12" t="n">
         <v>58</v>
@@ -18261,7 +18261,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>cubic_interpolation</t>
+          <t>spline_interpolation</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -18286,17 +18286,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>spline_interpolation</t>
+          <t>cubic_interpolation</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.667062</v>
+        <v>0.764224</v>
       </c>
       <c r="D19" t="n">
-        <v>0.769711</v>
+        <v>0.868886</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.406269</v>
+        <v>-0.792005</v>
       </c>
       <c r="F19" t="n">
         <v>86</v>
@@ -18586,17 +18586,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>cubic_interpolation</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2.762509</v>
+        <v>2.37209</v>
       </c>
       <c r="D31" t="n">
-        <v>3.098139</v>
+        <v>2.662934</v>
       </c>
       <c r="E31" t="n">
-        <v>-15.670821</v>
+        <v>-11.316183</v>
       </c>
       <c r="F31" t="n">
         <v>115</v>
@@ -18611,17 +18611,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>cubic_interpolation</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2.923715</v>
+        <v>2.762509</v>
       </c>
       <c r="D32" t="n">
-        <v>3.250883</v>
+        <v>3.098139</v>
       </c>
       <c r="E32" t="n">
-        <v>-17.355148</v>
+        <v>-15.670821</v>
       </c>
       <c r="F32" t="n">
         <v>115</v>
@@ -18815,13 +18815,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6.349068</v>
+        <v>4.536216</v>
       </c>
       <c r="D40" t="n">
-        <v>6.949935</v>
+        <v>5.05184</v>
       </c>
       <c r="E40" t="n">
-        <v>-79.24972099999999</v>
+        <v>-41.401493</v>
       </c>
       <c r="F40" t="n">
         <v>144</v>
@@ -18861,7 +18861,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>cubic_interpolation</t>
+          <t>spline_interpolation</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -18886,17 +18886,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>spline_interpolation</t>
+          <t>cubic_interpolation</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.722704</v>
+        <v>0.80515</v>
       </c>
       <c r="D43" t="n">
-        <v>0.818569</v>
+        <v>0.992051</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.049125</v>
+        <v>-0.540933</v>
       </c>
       <c r="F43" t="n">
         <v>173</v>
@@ -19190,13 +19190,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2.646819</v>
+        <v>1.927389</v>
       </c>
       <c r="D55" t="n">
-        <v>3.187375</v>
+        <v>2.234575</v>
       </c>
       <c r="E55" t="n">
-        <v>-11.400049</v>
+        <v>-5.094623</v>
       </c>
       <c r="F55" t="n">
         <v>202</v>
@@ -19415,13 +19415,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6.466504</v>
+        <v>4.038971</v>
       </c>
       <c r="D64" t="n">
-        <v>7.334357</v>
+        <v>4.886624</v>
       </c>
       <c r="E64" t="n">
-        <v>-35.167564</v>
+        <v>-15.055103</v>
       </c>
       <c r="F64" t="n">
         <v>230</v>
@@ -19616,28 +19616,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.219478</v>
+        <v>0.181154</v>
       </c>
       <c r="C5" t="n">
-        <v>0.410821</v>
+        <v>0.307639</v>
       </c>
       <c r="D5" t="n">
-        <v>0.667062</v>
+        <v>0.764224</v>
       </c>
       <c r="E5" t="n">
-        <v>2.923715</v>
+        <v>2.37209</v>
       </c>
       <c r="F5" t="n">
-        <v>6.349068</v>
+        <v>4.536216</v>
       </c>
       <c r="G5" t="n">
-        <v>0.722704</v>
+        <v>0.80515</v>
       </c>
       <c r="H5" t="n">
-        <v>2.646819</v>
+        <v>1.927389</v>
       </c>
       <c r="I5" t="n">
-        <v>6.466504</v>
+        <v>4.038971</v>
       </c>
     </row>
     <row r="6">
@@ -19825,10 +19825,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.0406</v>
+        <v>0.040592</v>
       </c>
       <c r="D2" t="n">
-        <v>0.050289</v>
+        <v>0.050278</v>
       </c>
       <c r="E2" t="n">
         <v>0.999283</v>
@@ -20025,10 +20025,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.048762</v>
+        <v>0.048758</v>
       </c>
       <c r="D10" t="n">
-        <v>0.06723999999999999</v>
+        <v>0.067235</v>
       </c>
       <c r="E10" t="n">
         <v>0.9986660000000001</v>
@@ -20221,7 +20221,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>cubic_interpolation</t>
+          <t>spline_interpolation</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -20246,14 +20246,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>spline_interpolation</t>
+          <t>cubic_interpolation</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.044815</v>
+        <v>0.04482</v>
       </c>
       <c r="D19" t="n">
-        <v>0.060635</v>
+        <v>0.060632</v>
       </c>
       <c r="E19" t="n">
         <v>0.99907</v>
@@ -20471,7 +20471,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>cubic_interpolation</t>
+          <t>spline_interpolation</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -20496,17 +20496,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>spline_interpolation</t>
+          <t>cubic_interpolation</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.084856</v>
+        <v>0.084893</v>
       </c>
       <c r="D29" t="n">
-        <v>0.142062</v>
+        <v>0.14191</v>
       </c>
       <c r="E29" t="n">
-        <v>0.995285</v>
+        <v>0.995295</v>
       </c>
       <c r="F29" t="n">
         <v>115</v>
@@ -20675,13 +20675,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.07883900000000001</v>
+        <v>0.078573</v>
       </c>
       <c r="D36" t="n">
-        <v>0.130379</v>
+        <v>0.130034</v>
       </c>
       <c r="E36" t="n">
-        <v>0.995847</v>
+        <v>0.995869</v>
       </c>
       <c r="F36" t="n">
         <v>144</v>
@@ -20875,13 +20875,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.087632</v>
+        <v>0.087411</v>
       </c>
       <c r="D44" t="n">
-        <v>0.132136</v>
+        <v>0.131854</v>
       </c>
       <c r="E44" t="n">
-        <v>0.995954</v>
+        <v>0.9959710000000001</v>
       </c>
       <c r="F44" t="n">
         <v>173</v>
@@ -21075,13 +21075,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.091271</v>
+        <v>0.091156</v>
       </c>
       <c r="D52" t="n">
-        <v>0.136509</v>
+        <v>0.136413</v>
       </c>
       <c r="E52" t="n">
-        <v>0.995627</v>
+        <v>0.995633</v>
       </c>
       <c r="F52" t="n">
         <v>202</v>
@@ -21275,13 +21275,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.105574</v>
+        <v>0.10548</v>
       </c>
       <c r="D60" t="n">
-        <v>0.156678</v>
+        <v>0.15663</v>
       </c>
       <c r="E60" t="n">
-        <v>0.994362</v>
+        <v>0.9943650000000001</v>
       </c>
       <c r="F60" t="n">
         <v>230</v>
@@ -21576,28 +21576,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.276524</v>
+        <v>0.231963</v>
       </c>
       <c r="C5" t="n">
-        <v>0.450142</v>
+        <v>0.351382</v>
       </c>
       <c r="D5" t="n">
-        <v>0.769711</v>
+        <v>0.868886</v>
       </c>
       <c r="E5" t="n">
-        <v>3.250883</v>
+        <v>2.662934</v>
       </c>
       <c r="F5" t="n">
-        <v>6.949935</v>
+        <v>5.05184</v>
       </c>
       <c r="G5" t="n">
-        <v>0.818569</v>
+        <v>0.992051</v>
       </c>
       <c r="H5" t="n">
-        <v>3.187375</v>
+        <v>2.234575</v>
       </c>
       <c r="I5" t="n">
-        <v>7.334357</v>
+        <v>4.886624</v>
       </c>
     </row>
     <row r="6">
@@ -21885,28 +21885,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.670743</v>
+        <v>0.768311</v>
       </c>
       <c r="C5" t="n">
-        <v>0.551572</v>
+        <v>0.726755</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.406269</v>
+        <v>-0.792005</v>
       </c>
       <c r="E5" t="n">
-        <v>-17.355148</v>
+        <v>-11.316183</v>
       </c>
       <c r="F5" t="n">
-        <v>-79.24972099999999</v>
+        <v>-41.401493</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.049125</v>
+        <v>-0.540933</v>
       </c>
       <c r="H5" t="n">
-        <v>-11.400049</v>
+        <v>-5.094623</v>
       </c>
       <c r="I5" t="n">
-        <v>-35.167564</v>
+        <v>-15.055103</v>
       </c>
     </row>
     <row r="6">
@@ -22194,28 +22194,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0406</v>
+        <v>0.040592</v>
       </c>
       <c r="C5" t="n">
-        <v>0.048762</v>
+        <v>0.048758</v>
       </c>
       <c r="D5" t="n">
-        <v>0.044815</v>
+        <v>0.04482</v>
       </c>
       <c r="E5" t="n">
-        <v>0.084856</v>
+        <v>0.084893</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07883900000000001</v>
+        <v>0.078573</v>
       </c>
       <c r="G5" t="n">
-        <v>0.087632</v>
+        <v>0.087411</v>
       </c>
       <c r="H5" t="n">
-        <v>0.091271</v>
+        <v>0.091156</v>
       </c>
       <c r="I5" t="n">
-        <v>0.105574</v>
+        <v>0.10548</v>
       </c>
     </row>
     <row r="6">
@@ -22503,28 +22503,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.050289</v>
+        <v>0.050278</v>
       </c>
       <c r="C5" t="n">
-        <v>0.06723999999999999</v>
+        <v>0.067235</v>
       </c>
       <c r="D5" t="n">
-        <v>0.060635</v>
+        <v>0.060632</v>
       </c>
       <c r="E5" t="n">
-        <v>0.142062</v>
+        <v>0.14191</v>
       </c>
       <c r="F5" t="n">
-        <v>0.130379</v>
+        <v>0.130034</v>
       </c>
       <c r="G5" t="n">
-        <v>0.132136</v>
+        <v>0.131854</v>
       </c>
       <c r="H5" t="n">
-        <v>0.136509</v>
+        <v>0.136413</v>
       </c>
       <c r="I5" t="n">
-        <v>0.156678</v>
+        <v>0.15663</v>
       </c>
     </row>
     <row r="6">
@@ -22821,19 +22821,19 @@
         <v>0.99907</v>
       </c>
       <c r="E5" t="n">
-        <v>0.995285</v>
+        <v>0.995295</v>
       </c>
       <c r="F5" t="n">
-        <v>0.995847</v>
+        <v>0.995869</v>
       </c>
       <c r="G5" t="n">
-        <v>0.995954</v>
+        <v>0.9959710000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.995627</v>
+        <v>0.995633</v>
       </c>
       <c r="I5" t="n">
-        <v>0.994362</v>
+        <v>0.9943650000000001</v>
       </c>
     </row>
     <row r="6">
@@ -23667,7 +23667,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>cubic_interpolation</t>
+          <t>spline_interpolation</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -23692,17 +23692,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>spline_interpolation</t>
+          <t>cubic_interpolation</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.144761</v>
+        <v>1.198896</v>
       </c>
       <c r="D29" t="n">
-        <v>1.38463</v>
+        <v>1.45074</v>
       </c>
       <c r="E29" t="n">
-        <v>0.228051</v>
+        <v>0.152577</v>
       </c>
       <c r="F29" t="n">
         <v>115</v>
@@ -23946,13 +23946,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.806596</v>
+        <v>1.806566</v>
       </c>
       <c r="D39" t="n">
-        <v>2.338891</v>
+        <v>2.338855</v>
       </c>
       <c r="E39" t="n">
-        <v>-8.150543000000001</v>
+        <v>-8.150264999999999</v>
       </c>
       <c r="F39" t="n">
         <v>144</v>
@@ -24471,13 +24471,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1.828572</v>
+        <v>1.828461</v>
       </c>
       <c r="D60" t="n">
-        <v>2.201069</v>
+        <v>2.200969</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.174731</v>
+        <v>-0.174625</v>
       </c>
       <c r="F60" t="n">
         <v>230</v>
@@ -24781,10 +24781,10 @@
         <v>0.488978</v>
       </c>
       <c r="E5" t="n">
-        <v>1.144761</v>
+        <v>1.198896</v>
       </c>
       <c r="F5" t="n">
-        <v>1.806596</v>
+        <v>1.806566</v>
       </c>
       <c r="G5" t="n">
         <v>1.805293</v>
@@ -24793,7 +24793,7 @@
         <v>1.774478</v>
       </c>
       <c r="I5" t="n">
-        <v>1.828572</v>
+        <v>1.828461</v>
       </c>
     </row>
     <row r="6">
@@ -25090,10 +25090,10 @@
         <v>0.549187</v>
       </c>
       <c r="E5" t="n">
-        <v>1.38463</v>
+        <v>1.45074</v>
       </c>
       <c r="F5" t="n">
-        <v>2.338891</v>
+        <v>2.338855</v>
       </c>
       <c r="G5" t="n">
         <v>2.267963</v>
@@ -25102,7 +25102,7 @@
         <v>2.054434</v>
       </c>
       <c r="I5" t="n">
-        <v>2.201069</v>
+        <v>2.200969</v>
       </c>
     </row>
     <row r="6">
@@ -25399,10 +25399,10 @@
         <v>0.599529</v>
       </c>
       <c r="E5" t="n">
-        <v>0.228051</v>
+        <v>0.152577</v>
       </c>
       <c r="F5" t="n">
-        <v>-8.150543000000001</v>
+        <v>-8.150264999999999</v>
       </c>
       <c r="G5" t="n">
         <v>-3.031298</v>
@@ -25411,7 +25411,7 @@
         <v>-1.762454</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.174731</v>
+        <v>-0.174625</v>
       </c>
     </row>
     <row r="6">

--- a/results/tablice/sve_tablice_rezultata.xlsx
+++ b/results/tablice/sve_tablice_rezultata.xlsx
@@ -1,33 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="sve_rezultate" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="random_detaljno" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="random_MAE" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="random_RMSE" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="random_R2" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="block_detaljno" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="block_MAE" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="block_RMSE" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="block_R2" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="block_start_detaljno" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="block_start_MAE" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="block_start_RMSE" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="block_start_R2" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="block_middle_detaljno" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="block_middle_MAE" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="block_middle_RMSE" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="block_middle_R2" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="block_end_detaljno" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="block_end_MAE" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="block_end_RMSE" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="block_end_R2" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sve_rezultate" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="random_detaljno" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="random_MAE" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="random_RMSE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="random_R2" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="block_detaljno" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="block_MAE" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="block_RMSE" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="block_R2" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="block_start_detaljno" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="block_start_MAE" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="block_start_RMSE" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="block_start_R2" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="block_middle_detaljno" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="block_middle_MAE" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="block_middle_RMSE" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="block_middle_R2" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="block_end_detaljno" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="block_end_MAE" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="block_end_RMSE" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="block_end_R2" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
